--- a/ig/DM_FINESS_New/CodeSystem-TRE-R75-InseeNAFrev2Niveau5.xlsx
+++ b/ig/DM_FINESS_New/CodeSystem-TRE-R75-InseeNAFrev2Niveau5.xlsx
@@ -37,7 +37,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>20251222120000</t>
+    <t>20260223120000</t>
   </si>
   <si>
     <t>Name</t>
@@ -64,7 +64,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-12-22T12:00:00+01:00</t>
+    <t>2026-02-23T12:00:00+01:00</t>
   </si>
   <si>
     <t>Publisher</t>
